--- a/inst/resources/tool_obs_water_point_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_water_point_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$118</definedName>
@@ -860,7 +860,21 @@
           <t>start</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>début</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>البداية</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>inicio</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>start</t>
@@ -881,7 +895,21 @@
           <t>end</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>النهاية</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>end</t>
@@ -902,7 +930,21 @@
           <t>today</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>aujourd’hui</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>اليوم</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hoy</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>today</t>
@@ -923,7 +965,21 @@
           <t>deviceid</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>identifiant de l’appareil</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>معرّف الجهاز</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>identificador del dispositivo</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>deviceid</t>
@@ -944,7 +1000,21 @@
           <t>audit</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>journal d’audit</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>سجل التدقيق</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>registro de auditoría</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>audit</t>
@@ -971,9 +1041,21 @@
           <t>date_survey</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la date de l’entretien ?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ما هو تاريخ المقابلة؟</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuál es la fecha de la entrevista?</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
@@ -1008,8 +1090,21 @@
           <t>enumerator</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer l’identifiant de l’enquêteur</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تحديد معرف الباحث الميداني</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Por favor indique el identificador del encuestador</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Please specify enumerator ID</t>
@@ -1033,8 +1128,21 @@
           <t>site1</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Veuillez indiquer le site de l’étude</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تحديد موقع الدراسة</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Por favor indique el sitio del estudio</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Please specify study site</t>
@@ -1058,8 +1166,24 @@
           <t>WASH_partner_yn</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Demandez aux personnes autour du point d’eau :
+Y a-t-il une ONG WASH ou un autre prestataire de services qui fournit un appui et assure l’entretien de ce point d’eau ?</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>اسأل الأشخاص الموجودين حول نقطة المياه:
+هل توجد منظمة غير حكومية في مجال المياه والصرف الصحي والنظافة أو مقدم خدمة آخر يقدم الدعم والصيانة لنقطة المياه هذه؟</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pregunte a las personas alrededor del punto de agua:
+¿Hay alguna ONG WASH u otro proveedor de servicios que brinde apoyo y mantenimiento a este punto de agua?</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Ask to the people around the water point: 
@@ -1084,9 +1208,22 @@
           <t>contact_WASH</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Contact du partenaire ONG WASH</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>جهة الاتصال لدى شريك منظمة WASH</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Contacto del socio ONG WASH</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Contact for WASH NGO Partner</t>
@@ -1115,8 +1252,24 @@
           <t>water_committee_yn</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Demandez aux personnes autour du point d’eau :
+Existe-t-il un comité de gestion de l’eau ou un autre groupe qui coordonne et appuie l’utilisation communautaire du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>اسأل الأشخاص الموجودين حول نقطة المياه:
+هل توجد لجنة لإدارة المياه أو مجموعة أخرى تنسق وتدعم استخدام المجتمع لنقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pregunte a las personas alrededor del punto de agua:
+¿Existe un comité de gestión del agua u otro grupo que coordine y apoye el uso comunitario del punto de agua?</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Ask to the people around the water point: 
@@ -1141,9 +1294,22 @@
           <t>contact_water</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Contact des comités de gestion de l’eau</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>جهة الاتصال لدى لجان إدارة المياه</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Contacto de los comités de gestión del agua</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Contact for Water Management Committees</t>
@@ -1172,21 +1338,34 @@
           <t>gps_coordinates</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Veuillez fournir les coordonnées GPS du lieu de l’entretien</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(Appuyer sur l'icône de détection de la position actuelle)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n"/>
+          <t>(Appuyez sur l’icône pour détecter la position actuelle)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>يرجى تقديم إحداثيات GPS لموقع المقابلة</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(انقر على أيقونة اكتشاف الموقع الحالي)</t>
+          <t>(اضغط على أيقونة تحديد الموقع الحالي)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Por favor proporcione las coordenadas GPS del lugar de la entrevista</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(Toca el icono para detectar la ubicación actual)</t>
+          <t>(Toque el icono para detectar la ubicación actual)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,8 +1396,21 @@
           <t>time</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Heure de l’observation</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>وقت الملاحظة</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hora de la observación</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Time of Observation</t>
@@ -1263,7 +1455,21 @@
           <t>water_obs_note</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Pour les questions suivantes, demandez les informations aux usagers et aux personnes se trouvant à proximité du point d’eau.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>بالنسبة للأسئلة التالية، اطلب المعلومات من مستخدمي نقطة المياه والأشخاص القريبين منها.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Para las siguientes preguntas, solicite la información a los usuarios y a las personas cercanas al punto de agua.</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">For the following questions, ask the users and nearby people to the waterpoint for the information. </t>
@@ -1284,8 +1490,21 @@
           <t>name</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le nom du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ما اسم نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>¿Cuál es el nombre del punto de agua?</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>What is the name of the water point?</t>
@@ -1309,9 +1528,36 @@
           <t>type_waterpoint</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le type de point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Fait référence à l’infrastructure ou au site observé où l’eau est stockée ou distribuée.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>ما نوع نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>يشير إلى البنية التحتية أو الموقع الذي تتم ملاحظته حيث يتم تخزين المياه أو توزيعها.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>¿Qué tipo de punto de agua es?</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Se refiere a la infraestructura o lugar observado donde se almacena o distribuye el agua.</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>What is the type of water point?</t>
@@ -1340,9 +1586,22 @@
           <t>type_waterpoint_other</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1371,9 +1630,36 @@
           <t>water_source</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la source de ce point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Fait référence à l’origine précise de l’eau au point d’eau, en répondant à la question : « D’où vient l’eau ? »</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ما هو مصدر المياه لهذه النقطة؟</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>يشير إلى المصدر المحدد للمياه عند نقطة المياه، للإجابة على السؤال: "من أين تأتي المياه؟"</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>¿Cuál es la fuente de este punto de agua?</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Se refiere al origen específico del agua en el punto de agua, respondiendo a la pregunta: "¿De dónde viene el agua?"</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>What is the source for this water point?</t>
@@ -1402,9 +1688,22 @@
           <t>water_source_other</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1433,9 +1732,36 @@
           <t>power_source</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Quelle est la principale source d’énergie ou de pompage ?</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>ما هو مصدر الطاقة أو التشغيل الرئيسي؟</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>¿Cuál es la principal fuente de energía o accionamiento?</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>What is the primary mover/power source?</t>
@@ -1464,10 +1790,36 @@
           <t>power_source_other</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1475,7 +1827,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="L24" t="b">
@@ -1501,13 +1853,36 @@
           <t>water_distribution</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Comment l’eau est-elle distribuée ou collectée à partir de ce point d’eau ?</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Sélectionnez tout ce qui s'y rapporte</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>كيف يتم توزيع المياه أو جمعها من نقطة المياه هذه؟</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>¿Cómo se distribuye o recoge el agua desde este punto de agua?</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>How is water distributed or collected from this water point?</t>
@@ -1536,9 +1911,22 @@
           <t>water_distribution_other</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="n"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -1567,8 +1955,21 @@
           <t>time_access</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>À partir de quelle heure les personnes peuvent-elles accéder au point d’eau au plus tôt ?</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>ما هو أبكر وقت يمكن فيه للناس الوصول إلى نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>¿Cuál es la hora más temprana en que las personas pueden acceder a este punto de agua?</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>What are the earliest hours that people can access this water point?</t>
@@ -1592,10 +1993,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -1618,8 +2033,21 @@
           <t>time_end</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Jusqu’à quelle heure les personnes peuvent-elles accéder au point d’eau au plus tard ?</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>ما هو آخر وقت يمكن فيه للناس الوصول إلى نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>¿Cuál es la hora más tardía en que las personas pueden acceder a este punto de agua?</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">What are the latest hours that people can access this water point? </t>
@@ -1664,9 +2092,21 @@
           <t>estimated_pop_covered</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Population estimée desservie par ce point d’eau</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>عدد السكان التقديري الذين تخدمهم نقطة المياه هذه</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Población estimada cubierta por este punto de agua</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Estimated population covered by this water point</t>
@@ -1695,9 +2135,36 @@
           <t>serve_markets</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ce point d’eau dessert-il un marché ?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>هل تخدم نقطة المياه هذه أي سوق؟</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>¿Este punto de agua abastece a algún mercado?</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Does the water point serve any market?</t>
@@ -1726,9 +2193,22 @@
           <t>serve_markets_type</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quel marché dessert-il ?</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، أي سوق تخدم؟</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="n"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿a qué mercado abastece?</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>If yes, which market does it serve?</t>
@@ -1757,9 +2237,36 @@
           <t>serve_health</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ce point d’eau dessert-il un établissement de santé ?</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>هل تخدم نقطة المياه هذه مرفقاً صحياً؟</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>¿Este punto de agua abastece a un establecimiento de salud?</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Does the water point serve a health facility?</t>
@@ -1788,9 +2295,22 @@
           <t>serve_health_type</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, lequel ?</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، أي مرفق؟</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="n"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿cuál?</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>If yes, which one?</t>
@@ -1819,9 +2339,36 @@
           <t>serve_watermgmt</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Le point d’eau est-il géré par un comité de gestion de l’eau ou lié à un tel comité ?</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>هل تتم إدارة نقطة المياه أو ربطها بأي لجنة لإدارة المياه؟</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>¿El punto de agua está gestionado o vinculado a algún comité de gestión del agua?</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Is the water point managed or linked with any water management committee?</t>
@@ -1850,9 +2397,22 @@
           <t>serve_watermgmt_type</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quel comité ?</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، أي لجنة؟</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="n"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿qué comité?</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, which committee? </t>
@@ -1881,9 +2441,36 @@
           <t>service_NGO</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Une ONG appuie-t-elle la construction ou l’entretien du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>هل تدعم أي منظمة غير حكومية بناء نقطة المياه أو صيانتها؟</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>¿Alguna ONG apoya la construcción o el mantenimiento del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Does any NGO support the building or maintenance of the water point?</t>
@@ -1912,9 +2499,22 @@
           <t>service_NGO_type</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quelle ONG ?</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، أي منظمة؟</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="n"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿qué ONG?</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>If yes, which NGO?</t>
@@ -1943,9 +2543,21 @@
           <t>queing</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Estimez le nombre de personnes faisant la queue au moment de l’observation.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>قدّر عدد الأشخاص المنتظرين في الطابور وقت الملاحظة.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Estime cuántas personas están haciendo cola en el momento de la observación.</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Estimate how many people are queing at the time of the observation.</t>
@@ -1974,9 +2586,36 @@
           <t>tension_visible</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il une foule visible, des tensions accrues ou des bagarres ?</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>هل يوجد ازدحام واضح أو توتر متزايد أو شجار؟</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>¿Hay hacinamiento visible, tensiones elevadas o peleas?</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">Is there any visible crowding, raised tensions, or fighting? </t>
@@ -2005,9 +2644,22 @@
           <t>tension</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, veuillez décrire.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>إذا كان الأمر كذلك، يرجى الوصف.</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="n"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Si es así, describa.</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">If so, please describe. </t>
@@ -2036,9 +2688,36 @@
           <t>waterpoint_fenced</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Le point d’eau est-il clôturé ?</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>هل نقطة المياه مسيّجة؟</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>¿El punto de agua está cercado?</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Is the water point fenced off?</t>
@@ -2067,8 +2746,21 @@
           <t>safety</t>
         </is>
       </c>
-      <c r="D44" s="11" t="n"/>
-      <c r="F44" s="2" t="n"/>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>D’après vos observations, l’emplacement du point d’eau semble-t-il sûr et situé à une distance appropriée des habitations ?</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>بناءً على ملاحظاتك، هل يبدو موقع نقطة المياه آمناً وموجوداً على مسافة مناسبة من المنازل؟</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Según sus observaciones, ¿la ubicación del punto de agua parece segura y situada a una distancia adecuada de las viviendas?</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Based on your observations, does the water point location appears safe and located at at appropriate distance from homes?</t>
@@ -2092,9 +2784,22 @@
           <t>safety_risks</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Si non, veuillez décrire les risques de protection que vous anticipez en raison de l’emplacement du point d’eau :</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة لا، يرجى وصف أي مخاطر حماية تتوقعها بسبب موقع نقطة المياه:</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="n"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Si la respuesta es no, describa cualquier riesgo de protección que prevea debido a la ubicación del punto de agua:</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>If no, please describe any protection risks that you foresee due to the location of the water point:</t>
@@ -2123,8 +2828,21 @@
           <t>accessibility</t>
         </is>
       </c>
-      <c r="D46" s="11" t="n"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>D’après vos observations, le point d’eau semble-t-il facilement accessible à tous les groupes de population, y compris les personnes en situation de handicap, les personnes âgées, les enfants, les femmes enceintes, etc. ?</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>بناءً على ملاحظاتك، هل تبدو نقطة المياه سهلة الوصول لجميع فئات السكان، بما في ذلك الأشخاص ذوو الإعاقة، وكبار السن، والأطفال، والنساء الحوامل، إلخ؟</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Según sus observaciones, ¿el punto de agua parece fácilmente accesible para todos los grupos de población, incluidas las personas con discapacidad, las personas mayores, los niños, las mujeres embarazadas, etc.?</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Based on your observations, does the water point appears to be easily accessible to all population groups, including people with disabilities, the elderly, children, pregnant women, etc.</t>
@@ -2148,9 +2866,22 @@
           <t>accessibility_limits</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Si non, veuillez expliquer pourquoi vous considérez qu’il n’est pas facilement accessible, en particulier pour certains groupes de population.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة لا، يرجى توضيح سبب اعتبارك أنه ليس سهل الوصول، خاصة لفئات سكانية معينة.</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="n"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Si la respuesta es no, explique por qué considera que no es fácilmente accesible, especialmente para grupos específicos de población.</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>If no, please describe why you consider that it is not easily accessible, especially for specific population groups.</t>
@@ -2179,10 +2910,36 @@
           <t>stagnant_water</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il de l’eau stagnante autour du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد مياه راكدة حول نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>¿Hay agua estancada alrededor del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Is there stagnant water around the water point?</t>
@@ -2198,7 +2955,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2216,9 +2973,22 @@
           <t>stagnant_water_image</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Veuillez prendre une photo claire de l’eau stagnante autour du point d’eau. Incluez le point d’eau dans la photo si possible.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>يرجى التقاط صورة واضحة للمياه الراكدة حول نقطة المياه. قم بإدراج نقطة المياه في الصورة إن أمكن.</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="n"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tome una foto clara del agua estancada alrededor del punto de agua. Incluya el punto de agua en la foto si es posible.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Please take a clear picture of the stagnant water around the water point. Include the water point in the picture if possible.</t>
@@ -2247,9 +3017,36 @@
           <t>animals_visible</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il des animaux visibles autour du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد حيوانات ظاهرة حول نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>¿Hay animales visibles alrededor del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Any visible animals staying around the water point?</t>
@@ -2278,9 +3075,22 @@
           <t>animals_image</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Veuillez prendre une photo claire des animaux près du point d’eau. Incluez le point d’eau dans la photo si possible.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>يرجى التقاط صورة واضحة للحيوانات بالقرب من نقطة المياه. قم بإدراج نقطة المياه في الصورة إن أمكن.</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="n"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tome una foto clara de los animales cerca del punto de agua. Incluya el punto de agua en la foto si es posible.</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Please take a clear picture of the animals near the water point. Include the water point in the picture if possible.</t>
@@ -2309,9 +3119,36 @@
           <t>garbage_feces</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il des déchets ou des excréments d’animaux visibles autour du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد نفايات أو براز حيوانات ظاهر حول نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>¿Hay basura o heces de animales visibles alrededor del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Any garbage or animal faeces visible around the water point?</t>
@@ -2340,9 +3177,22 @@
           <t>garbage_feces_image</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Veuillez prendre une photo claire des déchets ou des excréments d’animaux. Incluez le point d’eau dans la photo si possible.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>يرجى التقاط صورة واضحة للنفايات أو براز الحيوانات. قم بإدراج نقطة المياه في الصورة إن أمكن.</t>
+        </is>
+      </c>
       <c r="G53" s="2" t="n"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tome una foto clara de la basura o las heces de animales. Incluya el punto de agua en la foto si es posible.</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Please take a clear picture of the garbage or animal feces. Include the water point in the picture if possible.</t>
@@ -2371,9 +3221,36 @@
           <t>soil_characteristics</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Quelles sont les caractéristiques du sol autour du point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>ما هي خصائص التربة حول نقطة المياه؟</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>¿Cuáles son las características del suelo alrededor del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>What’s the characteristic of the soil around the water point?</t>
@@ -2402,9 +3279,22 @@
           <t>soil_characteristics_other</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="n"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -2433,9 +3323,36 @@
           <t>latrine_present</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il une latrine à moins de 30 mètres ?</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>هل توجد مرحاض على بعد أقل من 30 متراً؟</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>¿Hay alguna letrina a menos de 30 metros?</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>Any latrine within 30 meters?</t>
@@ -2464,11 +3381,36 @@
           <t>latrine_meters</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, à quelle distance en mètres ?</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Fournissez la meilleure estimation possible en mètres.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما المسافة بالأمتار؟</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>قدّم أفضل تقدير ممكن بالأمتار.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿a qué distancia en metros?</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Proporcione la mejor estimación posible en metros.</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, how far in meters? </t>
@@ -2507,8 +3449,21 @@
           <t>basic_functionality</t>
         </is>
       </c>
-      <c r="D58" s="11" t="n"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Veuillez effectuer des tests de fonctionnement de base du point de vue d’un usager (par exemple ouvrir les robinets, actionner la pompe) et inspecter visuellement les tuyaux. Le point d’eau fonctionne-t-il comme prévu au moment de l’observation ?</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>يرجى إجراء اختبارات وظيفية أساسية من منظور المستخدم (مثل فتح الصنابير أو تشغيل المضخة) وفحص الأنابيب بصرياً. هل تعمل نقطة المياه كما هو متوقع وقت الملاحظة؟</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Realice pruebas básicas de funcionamiento desde la perspectiva de un usuario (por ejemplo, abrir los grifos, accionar la bomba) e inspeccione visualmente las tuberías. ¿El punto de agua funciona como se espera en el momento de la observación?</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Please perform basic functionality tests from a user's perspective (e.g., opening the taps, operating the pump) and visually inspect the pipes. Does the water point function as expected at the time of the observation?</t>
@@ -2532,9 +3487,22 @@
           <t>functionality_details</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="F59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Si non, veuillez décrire tout problème rencontré :</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة لا، يرجى وصف أي مشكلة تمت مواجهتها:</t>
+        </is>
+      </c>
       <c r="G59" s="2" t="n"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Si la respuesta es no, describa cualquier problema encontrado:</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">If no, please describe any issue encountered: </t>
@@ -2563,9 +3531,36 @@
           <t>colour_odour_taste</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Veuillez verser un peu d’eau du point d’eau dans un verre ou une bouteille transparente. Y a-t-il une couleur, une odeur ou un goût perceptible ?</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>يرجى صب بعض المياه من نقطة المياه في كأس أو زجاجة شفافة. هل يوجد لون أو رائحة أو طعم ملحوظ؟</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vierta un poco de agua del punto de agua en un vaso o botella transparente. ¿Hay color, olor o sabor perceptible?</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">Please poor some of the water from the water point in a glass or transparent bottle. Any noticeable colour, odour or taste? </t>
@@ -2594,10 +3589,23 @@
           <t>colour_odour_taste_description</t>
         </is>
       </c>
-      <c r="D61" s="11" t="n"/>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Si oui, veuillez décrire :</t>
+        </is>
+      </c>
       <c r="E61" s="11" t="n"/>
-      <c r="F61" s="11" t="n"/>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، يرجى الوصف:</t>
+        </is>
+      </c>
       <c r="G61" s="11" t="n"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, describa:</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>If yes, please describe:</t>
@@ -2664,7 +3672,21 @@
           <t>note_flow_rate_1</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;**Débits**&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;**معدلات التدفق**&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;**Caudales**&lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;**Flow Rates**&lt;/span&gt;</t>
@@ -2685,7 +3707,24 @@
           <t>note_flow_rate_2</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Nous allons maintenant vous demander d’estimer ou de mesurer le débit du point d’eau au moment de l’observation.
+Dans la mesure du possible, les partenaires WASH doivent être sollicités pour appuyer une lecture au débitmètre ou une mesure volumétrique. Si cela n’est pas possible, une mesure manuelle doit être effectuée.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>سنطلب منك الآن تقدير أو قياس معدل تدفق نقطة المياه وقت الملاحظة.
+كلما أمكن، ينبغي طلب دعم شركاء المياه والصرف الصحي والنظافة لإجراء قراءة باستخدام مقياس التدفق أو قياس حجمي. إذا لم يكن ذلك ممكناً، يجب إجراء قياس يدوي.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ahora le pediremos que estime o mida el caudal del punto de agua en el momento de la observación.
+Siempre que sea posible, se debe solicitar apoyo a los socios WASH para realizar una lectura con caudalímetro o una medición volumétrica. Si esto no es posible, se debe realizar una medición manual.</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>We will now ask you to estimate or measure the flow rate of the water point at the time of observation.
@@ -2743,8 +3782,21 @@
           <t>estimate_yield_method</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Quelle méthode est utilisée pour estimer le débit ?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>ما الطريقة المستخدمة لتقدير الإنتاجية/التدفق؟</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>¿Qué método se utiliza para estimar el caudal?</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>What is the method used to estimate yield?</t>
@@ -2768,9 +3820,22 @@
           <t>estimate_yield_method_other</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G69" s="2" t="n"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -2814,8 +3879,25 @@
           <t>yield_note</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Pour estimer le débit de ce point d’eau, demandez à un usager si vous pouvez l’observer en train de remplir son récipient, ou demandez à emprunter un récipient d’eau à une personne à proximité. Vous observerez les usagers remplir leurs récipients ou remplirez directement un récipient vous-même.
+Vous répéterez ce processus 2 fois et les résultats seront moyennés. Cette étape peut prendre quelques minutes.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>لتقدير إنتاجية المياه في نقطة المياه هذه، اطلب من أحد المستخدمين السماح لك بمراقبته أثناء ملء المياه، أو اطلب استعارة وعاء مياه من شخص قريب. ستراقب المستخدمين وهم يملؤون أوعيتهم أو ستملأ وعاءً بنفسك مباشرة.
+ستكرر هذه العملية مرتين وسيتم حساب المتوسط. قد تستغرق هذه الخطوة بضع دقائق.</t>
+        </is>
+      </c>
       <c r="G71" s="2" t="n"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Para estimar el caudal de este punto de agua, pida a un usuario si puede observarlo mientras llena su recipiente, o pida prestado un recipiente de agua a alguien cercano. Observará a los usuarios llenando sus recipientes o llenará directamente un recipiente usted mismo.
+Repetirá este proceso 2 veces y se promediarán los resultados. Este paso puede tomar unos minutos.</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">To estimate the yield of water for this water point, please ask one of the water point users if you can observe them filling up their water, or ask to borrow a water container from someone nearby. ou will observe the users filling their water containers or directly fill a water container yourself. 
@@ -2911,7 +3993,21 @@
           <t>note_measurement_number</t>
         </is>
       </c>
-      <c r="D75" s="15" t="n"/>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt; **Mesure numéro ${container_position}**&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt; **القياس رقم ${container_position}**&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt; **Medición número ${container_position}**&lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt; **Measurement number ${container_position}**&lt;/span&gt;</t>
@@ -2932,9 +4028,36 @@
           <t>container_volume</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Quel est le volume approximatif &lt;span style="color:red"&gt;en litres&lt;/span&gt; du récipient d’eau pour la mesure n° ${container_position} ?</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Si ce n’est pas clair, demandez au répondant ou à la personne à qui vous empruntez le récipient. Sinon, fournissez votre meilleure estimation.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>ما هو الحجم التقريبي &lt;span style="color:red"&gt;باللترات&lt;/span&gt; لوعاء المياه للقياس رقم ${container_position}؟</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>إذا لم يكن الأمر واضحاً، اسأل المشارك أو الشخص الذي استعرت منه وعاء المياه. وإلا فقدم أفضل تقدير لديك.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>¿Cuál es el volumen aproximado &lt;span style="color:red"&gt;en litros&lt;/span&gt; del recipiente de agua para la medición n.º ${container_position}?</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Si no está claro, pregunte al encuestado o a la persona a quien le prestó el recipiente. De lo contrario, proporcione su mejor estimación.</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>What is the approximate volume &lt;span style="color:red"&gt; in liters &lt;/span&gt;of water container for measure # ${container_position}?</t>
@@ -2963,8 +4086,30 @@
           <t>container_time</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n"/>
-      <c r="F77" s="2" t="n"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Nous allons maintenant mesurer le nombre de secondes nécessaires pour remplir complètement le récipient. Commencez à compter lorsque le robinet ou la pompe est activé(e)/ouvert(e), et arrêtez lorsque le récipient est entièrement rempli.
+De préférence, utilisez un chronomètre (par exemple une application de téléphone). Sinon, comptez « un-mille », « deux-mille », « trois-mille » afin de maintenir un rythme correct en secondes.
+Si ce point d’eau est une pompe, assurez-vous qu’elle est actionnée à un rythme régulier et constant.
+&lt;span style="color:blue"&gt; Combien de secondes a-t-il fallu pour remplir complètement le récipient ? &lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>سنقيس الآن عدد الثواني اللازمة لملء الوعاء بالكامل. ابدأ العد عند تشغيل/فتح الصنبور أو المضخة، وتوقف عندما يمتلئ الوعاء تماماً.
+يفضل استخدام مؤقت/كرونومتر (مثل تطبيق الهاتف). وإذا لم يكن ذلك ممكناً، عدّ بطريقة منتظمة مثل: «ألف وواحد»، «ألف واثنان»، «ألف وثلاثة» لضمان حساب الثواني بوتيرة صحيحة.
+إذا كانت نقطة المياه تعمل بمضخة، تأكد من تشغيلها بوتيرة ثابتة ومنتظمة.
+&lt;span style="color:blue"&gt; كم ثانية استغرق ملء الوعاء بالكامل؟ &lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ahora mediremos cuántos segundos tarda el recipiente en llenarse completamente. Empiece a contar cuando se active/abra el grifo o la bomba, y deténgase cuando el recipiente esté completamente lleno.
+Preferiblemente, use un cronómetro (por ejemplo, una aplicación del teléfono). De lo contrario, cuente como «uno mil», «dos mil», «tres mil» para asegurarse de mantener el ritmo correcto en segundos.
+Si este punto de agua es una bomba, asegúrese de que se accione a un ritmo constante y uniforme.
+&lt;span style="color:blue"&gt; ¿Cuántos segundos tardó en llenarse completamente el recipiente? &lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>We will now measure how many seconds it takes for the container to completely fill. Start counting when the water tap/pump is activated/opened, and stop counting once the container is entirely filled. 
@@ -3127,9 +4272,42 @@
           <t>estimate_yield</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Pouvez-vous confirmer que les valeurs ci-dessous semblent exactes sur la base de vos mesures ?
+Litres moyens par seconde : ${calc_liters_per_second} litres par seconde
+Litres moyens par minute : ${calc_liters_per_minute} litres par minute</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Si c’est incorrect, veuillez revenir en arrière et vérifier que vos saisies sont exactes, ou refaire les deux mesures.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>هل يمكنك تأكيد أن القيم أدناه تبدو دقيقة بناءً على قياساتك؟
+متوسط اللترات في الثانية: ${calc_liters_per_second} لتر/ثانية
+متوسط اللترات في الدقيقة: ${calc_liters_per_minute} لتر/دقيقة</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>إذا كانت غير صحيحة، يرجى الرجوع والتحقق من دقة المدخلات، أو إعادة القياسين.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>¿Puede confirmar que los valores siguientes parecen correctos según sus mediciones?
+Litros promedio por segundo: ${calc_liters_per_second} litros por segundo
+Litros promedio por minuto: ${calc_liters_per_minute} litros por minuto</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Si es incorrecto, vuelva atrás y verifique que sus datos sean correctos, o repita las dos mediciones.</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>Can you confirm the below appear accurate based on your measures? 
@@ -3204,8 +4382,21 @@
           <t>unit_yield</t>
         </is>
       </c>
-      <c r="D88" s="8" t="n"/>
-      <c r="F88" s="2" t="n"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Dans quelle unité le partenaire mesure-t-il le débit ?</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>بأي وحدة يقيس الشريك التدفق؟</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>¿En qué unidad mide el caudal el socio?</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">In which unit is the partner measuring the flow? </t>
@@ -3229,9 +4420,22 @@
           <t>measured_yield_per_min</t>
         </is>
       </c>
-      <c r="D89" s="8" t="n"/>
-      <c r="F89" s="2" t="n"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Veuillez saisir le débit mesuré au débitmètre ou par mesure volumétrique (en litres par minute) :</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>يرجى إدخال معدل التدفق المقاس بواسطة مقياس التدفق أو القياسات الحجمية (باللترات في الدقيقة):</t>
+        </is>
+      </c>
       <c r="G89" s="2" t="n"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ingrese el caudal medido con el medidor o mediante mediciones volumétricas (en litros por minuto):</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>Please enter the Flow rate measured with the meter or volumetric measurements (in Liters per Minute):</t>
@@ -3260,9 +4464,22 @@
           <t>measured_yield_per_sec</t>
         </is>
       </c>
-      <c r="D90" s="8" t="n"/>
-      <c r="F90" s="2" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Veuillez saisir le débit mesuré au débitmètre ou par mesure volumétrique (en litres par seconde) :</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>يرجى إدخال معدل التدفق المقاس بواسطة مقياس التدفق أو القياسات الحجمية (باللترات في الثانية):</t>
+        </is>
+      </c>
       <c r="G90" s="2" t="n"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ingrese el caudal medido con el medidor o mediante mediciones volumétricas (en litros por segundo):</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>Please enter the Flow rate measured with the meter or volumetric measurements (in Liters per Seconde):</t>
@@ -3369,7 +4586,21 @@
           <t>note_kii</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Nous souhaiterions maintenant poser des questions supplémentaires à un membre du personnel d’une ONG WASH ou à un prestataire de services disposant des connaissances techniques requises et connaissant ce point d’eau.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>نود الآن طرح أسئلة إضافية على أحد موظفي منظمة WASH غير الحكومية أو مقدم خدمة لديه المعرفة الفنية المطلوبة وملمّ بنقطة المياه هذه.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ahora nos gustaría hacer preguntas adicionales a un miembro del personal de una ONG WASH o proveedor de servicios que tenga los conocimientos técnicos necesarios y esté familiarizado con este punto de agua.</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">Now we would like to ask additional question to a WASH NGO staff or service provider who have the required technical knowledge and are familiar with this water point. </t>
@@ -3392,8 +4623,21 @@
           <t>kii_available</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;Y a-t-il un membre du personnel d’une ONG WASH ou d’un prestataire de services qui puisse vous renseigner sur les résultats de qualité de l’eau ou les besoins de réhabilitation de ce point d’eau ? &lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;هل يوجد موظف من منظمة WASH غير حكومية أو مقدم خدمة يمكنه إخبارك بنتائج جودة المياه أو احتياجات إعادة تأهيل نقطة المياه هذه؟ &lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>&lt;span style="color:blue"&gt;¿Hay algún miembro del personal de una ONG WASH o proveedor de servicios que pueda informarle sobre los resultados de calidad del agua o las necesidades de rehabilitación de este punto de agua? &lt;/span&gt;</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>&lt;span style="color:blue"&gt;Is there any WASH NGO or service provider staff member who can tell you about water quality results or rehabilitation needs for this water point? &lt;/span&gt;</t>
@@ -3419,8 +4663,22 @@
           <t>WASH_NGO_technical</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Section 4 : Questions techniques pour l’ONG WASH (complémentaires)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>القسم 4: أسئلة فنية لمنظمة WASH غير الحكومية (تكميلية)</t>
+        </is>
+      </c>
       <c r="G97" s="3" t="n"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sección 4: Preguntas técnicas para ONG WASH (complementarias)</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>Section 4: WASH NGO Technical Questions (supplemental)</t>
@@ -3448,9 +4706,48 @@
           <t>consent</t>
         </is>
       </c>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Je m’appelle __ et je travaille pour REACH Initiative, une organisation sœur d’ACTED, une organisation internationale à but non lucratif opérant dans cette zone.
+Nous réalisons une évaluation d’urgence afin de comprendre les besoins et priorités en santé publique de la population.
+Nous vous approchons aujourd’hui car nous souhaitons vous poser quelques questions sur votre perception des besoins de la communauté. Vos réponses seront partagées avec les acteurs humanitaires afin d’orienter leurs interventions. Auriez-vous 30 minutes pour participer à un entretien ?
+Il n’y a aucun avantage direct pour vous ou votre communauté à participer à cet entretien, et rien de ce que vous direz n’aura d’impact négatif sur votre accès à l’aide humanitaire. Votre participation est entièrement volontaire. Si vous vous sentez mal à l’aise à tout moment, dites-le-nous et nous arrêterons l’entretien. Toutes vos réponses resteront aussi confidentielles que possible.
+Le répondant accepte-t-il de poursuivre l’entretien ? [OUI / NON]</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>اسمي __ وأعمل مع مبادرة REACH، وهي منظمة شريكة لـ ACTED، وهي منظمة دولية غير ربحية تعمل في هذه المنطقة.
+نقوم بإجراء تقييم طارئ لفهم احتياجات وأولويات الصحة العامة للسكان.
+نتواصل معك اليوم لأننا نرغب في طرح بعض الأسئلة حول تصورك لاحتياجات المجتمع. سيتم مشاركة إجاباتك مع الجهات الإنسانية لدعم تخطيط أنشطتها. هل لديك 30 دقيقة للمشاركة في مقابلة؟
+لا توجد أي فائدة مباشرة لك أو لمجتمعك من المشاركة في هذه المقابلة، ولن يؤثر أي شيء تقوله سلباً على قدرتك على الحصول على المساعدة الإنسانية. مشاركتك طوعية تماماً. إذا شعرت بعدم الارتياح في أي وقت، أخبرنا وسنوقف المقابلة. سيتم الحفاظ على سرية جميع إجاباتك قدر الإمكان.
+هل يوافق المشارك على المتابعة؟ [نعم / لا]</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Mi nombre es __ y trabajo con REACH Initiative, una organización asociada a ACTED, una organización internacional sin fines de lucro que trabaja en esta zona.
+Estamos realizando una evaluación de emergencia para comprender las necesidades y prioridades de salud pública de la población.
+Nos acercamos a usted hoy porque queremos hacerle algunas preguntas sobre su percepción de las necesidades de la comunidad. Sus respuestas serán compartidas con actores humanitarios para orientar sus actividades. ¿Tendría 30 minutos para participar en una entrevista?
+No hay ningún beneficio directo para usted o su comunidad por participar en esta entrevista, y nada de lo que diga afectará negativamente su acceso a la asistencia humanitaria. Su participación es completamente voluntaria. Si se siente incómodo/a en cualquier momento, díganoslo y detendremos la entrevista. Todas sus respuestas se mantendrán lo más confidenciales posible.
+¿El encuestado acepta continuar con la entrevista? [SÍ / NO]</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>My name is __ and I am working with REACH, a sister organization to ACTED, an international non-profit organization working in this area. We are doing an emergency assessment to understand the public health needs and priorities for the population. We are approaching you today because we want to ask you about your perception of the communities needs. Your responses will be shared with humanitarian actors to inform their activities. Would you have 30 minutes to participate in an interview?
@@ -3504,9 +4801,21 @@
           <t>date</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Quand le test de qualité de l’eau le plus récent a-t-il été effectué pour ce point d’eau, le cas échéant ?</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>متى تم إجراء أحدث اختبار لجودة المياه لنقطة المياه هذه، إن وجد؟</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuándo se realizó la prueba de calidad del agua más reciente para este punto de agua, si se realizó alguna?</t>
+        </is>
+      </c>
       <c r="I100" s="2" t="n"/>
       <c r="J100" t="inlineStr">
         <is>
@@ -3541,9 +4850,36 @@
           <t>share_results</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Pouvez-vous partager les résultats de ce test ?</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>هل يمكنك مشاركة نتائج ذلك الاختبار؟</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>¿Puede compartir los resultados de esa prueba?</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>Can you share the results of that test?</t>
@@ -3593,10 +4929,36 @@
           <t>conductivity_test</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Tests de conductivité</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Cible : entre 1 000 et 1 500 μS/cm</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>اختبارات التوصيلية</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>الهدف: بين 1,000 و1,500 ميكروسيمنز/سم</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Pruebas de conductividad</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Objetivo: entre 1.000 y 1.500 μS/cm</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>Conductivity tests</t>
@@ -3630,10 +4992,36 @@
           <t>turbidity_test</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Turbidité</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Cible : ≤ 5 NTU</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>العكارة</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>الهدف: ≤ 5 NTU</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Turbidez</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Objetivo: ≤ 5 NTU</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>Turbidity</t>
@@ -3667,10 +5055,39 @@
           <t>PH_test</t>
         </is>
       </c>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="n"/>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="2" t="n"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Niveaux de pH</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Cible : pH 6,5 &lt; pH &lt; 8,5
+(non fondée sur un critère sanitaire)</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>مستويات الرقم الهيدروجيني</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>الهدف: pH 6.5 &lt; pH &lt; 8.5
+(ليس هدفاً قائماً على الصحة)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Niveles de pH</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Objetivo: pH 6,5 &lt; pH &lt; 8,5
+(no es un objetivo basado en salud)</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>pH levels</t>
@@ -3705,10 +5122,36 @@
           <t>faecal_test</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Coliformes fécaux</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Cible : 0 UFC/100 ml (unités formant colonies)</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>القولونيات البرازية</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>الهدف: 0 وحدة تشكيل مستعمرات/100 مل</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Coliformes fecales</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Objetivo: 0 UFC/100 ml (unidades formadoras de colonias)</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Faecal coliforms</t>
@@ -3742,10 +5185,36 @@
           <t>chlorine_test</t>
         </is>
       </c>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Chlore libre</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Cible : chlore libre (lorsque le chlore est utilisé comme désinfectant) après 30 minutes de contact au pH indiqué</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>الكلور الحر</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>الهدف: الكلور الحر (عند استخدام الكلور كمطهر) بعد 30 دقيقة من وقت التلامس عند قيمة pH</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Cloro libre</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Objetivo: cloro libre (cuando se usa cloro como desinfectante) después de 30 minutos de contacto al pH indicado</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>Free chlorine</t>
@@ -3794,9 +5263,36 @@
           <t>rehab_waterpoint</t>
         </is>
       </c>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="n"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Une réhabilitation est-elle nécessaire pour le point d’eau ?</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>هل تحتاج نقطة المياه إلى أي إعادة تأهيل؟</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>¿Se necesita alguna rehabilitación del punto de agua?</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Is any rehabilitation needed for the water point?</t>
@@ -3825,9 +5321,22 @@
           <t>rehab_waterpoint_other</t>
         </is>
       </c>
-      <c r="D110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G110" s="2" t="n"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -3856,14 +5365,36 @@
           <t>type_rehab_waterpoint</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quel type de réhabilitation ?</t>
+        </is>
+      </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Sélectionnez tout ce qui s'y rapporte</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما نوع إعادة التأهيل؟</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿qué tipo de rehabilitación?</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, what type of rehabilitation? </t>
@@ -3897,9 +5428,22 @@
           <t>type_rehab_waterpoint_other</t>
         </is>
       </c>
-      <c r="D112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G112" s="2" t="n"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -3928,9 +5472,36 @@
           <t>rehab_waternetwork</t>
         </is>
       </c>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="2" t="n"/>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Une réhabilitation est-elle nécessaire pour le réseau d’eau ?</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Sélectionnez une réponse</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>هل تحتاج شبكة المياه إلى أي إعادة تأهيل؟</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>اختر إجابة واحدة</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>¿Se necesita alguna rehabilitación de la red de agua?</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Seleccione una opción</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve"> Is any rehabilitation needed for the water network?</t>
@@ -3959,14 +5530,36 @@
           <t>type_rehab_waternetwork</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Si oui, quel type de réhabilitation ?</t>
+        </is>
+      </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Sélectionnez tout ce qui s'y rapporte</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
+          <t>Sélectionnez toutes les réponses applicables</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>إذا كانت الإجابة نعم، ما نوع إعادة التأهيل؟</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>اختر كل ما ينطبق</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Si la respuesta es sí, ¿qué tipo de rehabilitación?</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Seleccione todas las opciones que correspondan</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">If yes, what type of rehabilitation? </t>
@@ -4000,9 +5593,22 @@
           <t>type_rehab_waternetwork_other</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="n"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>other, specify</t>
@@ -4065,7 +5671,21 @@
           <t>comment</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Y a-t-il d’autres commentaires ou observations sur l’état ou la qualité de ce point d’eau ?</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>هل توجد أي تعليقات أو ملاحظات أخرى حول حالة أو جودة نقطة المياه هذه؟</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>¿Hay algún otro comentario u observación sobre el estado o la calidad de este punto de agua?</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">Is there any other comment or observation on the status or quality of this water point? </t>
@@ -4151,17 +5771,27 @@
     <row r="195"/>
     <row r="196"/>
     <row r="197">
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="C197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="D198" s="2" t="n"/>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -4538,12 +6168,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>رفض الإجابة</t>
+          <t>أفضل عدم الإجابة</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Se niega a responder</t>
+          <t>Prefiere no responder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5326,7 +6956,21 @@
           <t>hand_dug</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n"/>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Puits creusé à la main / puits non protégé</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>بئر محفور يدوياً / بئر غير محمي</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pozo excavado a mano / pozo no protegido</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Hand dug well / Unprotected well</t>
@@ -5349,17 +6993,17 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Forage / Puits protégé</t>
+          <t>Forage / puits protégé</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>بئر محفورة / بئر محمية</t>
+          <t>بئر محفور / بئر محمي</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pozo perforado / Pozo protegido</t>
+          <t>Pozo perforado / pozo protegido</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5370,7 +7014,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5388,7 +7032,21 @@
           <t>spring_protected</t>
         </is>
       </c>
-      <c r="D35" s="11" t="n"/>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Source protégée</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>نبع محمي</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Manantial protegido</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Protected Spring</t>
@@ -5409,7 +7067,21 @@
           <t>spring_unprotected</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n"/>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Source non protégée</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>نبع غير محمي</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Manantial no protegido</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Unprotected Spring</t>
@@ -5430,7 +7102,21 @@
           <t>reservoir</t>
         </is>
       </c>
-      <c r="D37" s="11" t="n"/>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Réservoir / citerne</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>خزان / صهريج</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Reservorio / tanque</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Reservoir / Tank</t>
@@ -5451,7 +7137,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5472,7 +7172,21 @@
           <t>surface_water</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Eau de surface</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>مياه سطحية</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Agua superficial</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Surface water</t>
@@ -5493,7 +7207,21 @@
           <t>rain_water</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Eau de pluie</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>مياه الأمطار</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Agua de lluvia</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Rain water</t>
@@ -5514,7 +7242,21 @@
           <t>underground_water</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Eau souterraine</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>مياه جوفية</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Agua subterránea</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Underground water</t>
@@ -5535,7 +7277,21 @@
           <t>water_trucking</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Approvisionnement par camion-citerne</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>نقل المياه بالصهاريج</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Camión cisterna</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Water trucking</t>
@@ -5591,7 +7347,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5612,7 +7382,21 @@
           <t>solar</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Solaire</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>طاقة شمسية</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Solar</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Solar</t>
@@ -5675,12 +7459,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>مدمج (ثنائي المصدر)</t>
+          <t>مشترك (مصدران)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Combinado (fuente dual)</t>
+          <t>Combinado (doble fuente)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5738,7 +7522,21 @@
           <t>manual</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>يدوي</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Manual</t>
@@ -5759,7 +7557,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5780,7 +7592,21 @@
           <t>piped_to_households</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Réseau canalisé vers les ménages</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>شبكة أنابيب إلى الأسر</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sistema entubado a hogares</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Piped system to households</t>
@@ -5808,7 +7634,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>نقاط مياه مجتمعية</t>
+          <t>صنابير جماعية</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5836,7 +7662,21 @@
           <t>stored_in_tank</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Stockée dans un réservoir</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>مخزنة في خزان</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Almacenada en tanque</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Stored in tank</t>
@@ -5869,7 +7709,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Balde y cuerda</t>
+          <t>Cubo y cuerda</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5892,7 +7732,21 @@
           <t>jerry_cans_buckets</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Jerricans ou seaux</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>جراكن أو دلاء</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bidones o cubos</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Jerry cans or buckets</t>
@@ -5913,7 +7767,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -5934,7 +7802,21 @@
           <t>rock_gravel</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Roche / gravier</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>صخور / حصى</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Roca / grava</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Rock/Gravel</t>
@@ -5990,7 +7872,21 @@
           <t>silt_fineearth</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Limon / terre fine</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>طمي / تربة ناعمة</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Limo / tierra fina</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Silt/ Fine Earth</t>
@@ -6011,7 +7907,21 @@
           <t>sand_sediment</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Sable / sédiments</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>رمل / رواسب</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Arena / sedimento</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>Sand/ Sediment</t>
@@ -6067,7 +7977,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -6090,17 +8014,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Lecture du compteur d'eau ou mesures volumétriques rapportées par le partenaire WASH</t>
+          <t>Lecture au débitmètre ou mesures volumétriques rapportées par le partenaire WASH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>قراءة عداد التدفق أو القياسات الحجمية من شريك WASH</t>
+          <t>قراءة مقياس التدفق أو القياسات الحجمية التي أبلغ عنها شريك WASH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lectura del contador de caudal reportada por el socio de WASH</t>
+          <t>Lectura de caudalímetro o mediciones volumétricas reportadas por el socio WASH</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6123,7 +8047,21 @@
           <t>manual_bucket</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Mesure manuelle (seau)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>قياس يدوي (دلو)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Medición manual (cubo)</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Manual Measurement (Bucket)</t>
@@ -6144,7 +8082,21 @@
           <t>no_equipment</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Aucun équipement pour mesurer le débit</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>لا توجد معدات لقياس التدفق</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sin equipo para medir el caudal</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>No Equipment to Measure the Yield</t>
@@ -6165,7 +8117,21 @@
           <t>dont_know</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ne sait pas</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>لا أعرف</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>No sabe</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Don’t Know</t>
@@ -6186,7 +8152,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -6209,17 +8189,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Nettoyage et vidange</t>
+          <t>Nettoyage et vidange des boues</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>التنظيف وإزالة الحمأة</t>
+          <t>تنظيف وإزالة الحمأة</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Limpieza y vaciado de lodos</t>
+          <t>Limpieza y desazolve</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6242,7 +8222,21 @@
           <t>structural_repairs</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Réparations structurelles</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>إصلاحات هيكلية</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Reparaciones estructurales</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>Structural repairs</t>
@@ -6265,17 +8259,17 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Revêtement et doublure</t>
+          <t>Revêtement et doublage</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>الطلاء والبطانة</t>
+          <t>طلاء وتبطين</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revestimiento y forro</t>
+          <t>Revestimiento y recubrimiento</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6298,7 +8292,21 @@
           <t>replacing_tank_components</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Remplacement de composants du réservoir</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>استبدال مكونات الخزان</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Reemplazo de componentes del tanque</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>Replacing tank components</t>
@@ -6319,7 +8327,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -6340,7 +8362,21 @@
           <t>well_development</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Développement du puits</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>تطوير البئر</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Desarrollo del pozo</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">Well development </t>
@@ -6361,7 +8397,21 @@
           <t>well_head_construction</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Construction de la tête de puits</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>إنشاء رأس البئر</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Construcción de la boca del pozo</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>Well head construction</t>
@@ -6382,7 +8432,21 @@
           <t>pipeline</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Canalisation</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>خط أنابيب</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tubería</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Pipeline</t>
@@ -6403,7 +8467,21 @@
           <t>installation_lifting_devices</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Installation de dispositifs de pompage avec sources d’énergie</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>تركيب أجهزة رفع/ضخ مع مصادر طاقة</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Instalación de dispositivos de elevación con fuentes de energía</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>Installation Lifting Devices with Power Sources</t>
@@ -6424,7 +8502,21 @@
           <t>water_tanks</t>
         </is>
       </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Réservoirs d’eau</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>خزانات مياه</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tanques de agua</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Water Tanks</t>
@@ -6445,7 +8537,21 @@
           <t>water_points</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Points d’eau</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>نقاط مياه</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Puntos de agua</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>Water points</t>
@@ -6466,7 +8572,21 @@
           <t>other</t>
         </is>
       </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Autre, veuillez préciser</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>أخرى، يرجى التحديد</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Otro, especifique</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Other, specify</t>
@@ -6487,7 +8607,21 @@
           <t>liters_per_min</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Litres par minute</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>لترات في الدقيقة</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Litros por minuto</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>Liters per Minute</t>
@@ -6508,7 +8642,21 @@
           <t>liters_per_sec</t>
         </is>
       </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Litres par seconde</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>لترات في الثانية</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Litros por segundo</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>Liters per Second</t>

--- a/inst/resources/tool_obs_water_point_iphra_v2.xlsx
+++ b/inst/resources/tool_obs_water_point_iphra_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'survey'!$B$1:$M$118</definedName>
@@ -767,42 +767,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>hint::French (fr)</t>
+          <t>hint::French</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>hint::Arabic (ar)</t>
+          <t>hint::Arabic</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>hint::Spanish (sp)</t>
+          <t>hint::Spanish</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>hint::English (en)</t>
+          <t>hint::English</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="L24" t="b">
@@ -1995,22 +1995,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -5692,106 +5692,28 @@
         </is>
       </c>
     </row>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
     <row r="197">
       <c r="C197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -5848,22 +5770,22 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>label::French (fr)</t>
+          <t>label::French</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>label::Arabic (ar)</t>
+          <t>label::Arabic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>label::Spanish (sp)</t>
+          <t>label::Spanish</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>label::English (en)</t>
+          <t>label::English</t>
         </is>
       </c>
     </row>
@@ -7014,7 +6936,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -8724,7 +8646,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>English (en)</t>
+          <t>English</t>
         </is>
       </c>
     </row>
